--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.95198615981909</v>
+        <v>8.929697750970602</v>
       </c>
       <c r="D2" t="n">
-        <v>54.98062526471986</v>
+        <v>8.934351605516978</v>
       </c>
       <c r="E2" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F2" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.18833237554078</v>
+        <v>6.368104011025377</v>
       </c>
       <c r="D3" t="n">
-        <v>39.09281682801736</v>
+        <v>6.35258273455282</v>
       </c>
       <c r="E3" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F3" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.34979629486106</v>
+        <v>6.231841897914922</v>
       </c>
       <c r="D4" t="n">
-        <v>38.6414702252119</v>
+        <v>6.279238911596934</v>
       </c>
       <c r="E4" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F4" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.54555426928951</v>
+        <v>0.9011525687595454</v>
       </c>
       <c r="D5" t="n">
-        <v>5.054675656125951</v>
+        <v>0.8213847941204672</v>
       </c>
       <c r="E5" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F5" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.784961343615366</v>
+        <v>0.615056218337497</v>
       </c>
       <c r="D6" t="n">
-        <v>3.114878339164725</v>
+        <v>0.5061677301142677</v>
       </c>
       <c r="E6" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F6" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.04949046116492</v>
+        <v>5.2080421999393</v>
       </c>
       <c r="D7" t="n">
-        <v>32.48851561241066</v>
+        <v>5.279383787016732</v>
       </c>
       <c r="E7" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F7" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.31722278079034</v>
+        <v>1.839048701878431</v>
       </c>
       <c r="D8" t="n">
-        <v>11.55764957446203</v>
+        <v>1.87811805585008</v>
       </c>
       <c r="E8" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F8" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.37510733740049</v>
+        <v>7.698454942327579</v>
       </c>
       <c r="D9" t="n">
-        <v>46.7548361899804</v>
+        <v>7.597660880871816</v>
       </c>
       <c r="E9" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F9" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.79359955088415</v>
+        <v>6.791459927018674</v>
       </c>
       <c r="D10" t="n">
-        <v>42.42603668137196</v>
+        <v>6.894230960722944</v>
       </c>
       <c r="E10" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F10" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>60.32127025303246</v>
+        <v>9.802206416117775</v>
       </c>
       <c r="D11" t="n">
-        <v>59.69489105764902</v>
+        <v>9.700419796867966</v>
       </c>
       <c r="E11" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F11" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.4596446536888</v>
+        <v>6.73719225622443</v>
       </c>
       <c r="D12" t="n">
-        <v>41.74670061135399</v>
+        <v>6.783838849345024</v>
       </c>
       <c r="E12" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F12" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>61.98471986558574</v>
+        <v>10.07251697815768</v>
       </c>
       <c r="D13" t="n">
-        <v>61.50501820244694</v>
+        <v>9.994565457897629</v>
       </c>
       <c r="E13" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F13" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>66.22891642881943</v>
+        <v>10.76219891968316</v>
       </c>
       <c r="D14" t="n">
-        <v>66.48063320656142</v>
+        <v>10.80310289606623</v>
       </c>
       <c r="E14" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F14" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74.86916754051103</v>
+        <v>12.16623972533304</v>
       </c>
       <c r="D15" t="n">
-        <v>75.1913127941218</v>
+        <v>12.21858832904479</v>
       </c>
       <c r="E15" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F15" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>71.28745800756791</v>
+        <v>11.58421192622979</v>
       </c>
       <c r="D16" t="n">
-        <v>71.38078597869935</v>
+        <v>11.59937772153864</v>
       </c>
       <c r="E16" t="n">
-        <v>22.03053991163499</v>
+        <v>3.579962735640687</v>
       </c>
       <c r="F16" t="n">
-        <v>22.11497829751287</v>
+        <v>3.59368397334584</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
